--- a/ex1.xlsx
+++ b/ex1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sangsin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sangsin\sangsin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9624865A-FF67-4A57-BA35-CD13248FDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF01CF1-E301-44DA-8E02-7D57C04CEDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8850" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{84958FD7-B295-4487-ADF9-123BC1CF77F4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84958FD7-B295-4487-ADF9-123BC1CF77F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>บริการ</t>
   </si>
@@ -126,6 +126,24 @@
   </si>
   <si>
     <t>old image restoration</t>
+  </si>
+  <si>
+    <t>2.5"</t>
+  </si>
+  <si>
+    <t>Width (cm)</t>
+  </si>
+  <si>
+    <t>Height (cm)</t>
+  </si>
+  <si>
+    <t>Width (px)</t>
+  </si>
+  <si>
+    <t>Height (px)</t>
+  </si>
+  <si>
+    <t>PHOTO ID SIZE</t>
   </si>
 </sst>
 </file>
@@ -133,9 +151,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_([$THB]\ * #,##0_);_([$THB]\ * \(#,##0\);_([$THB]\ * &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_([$THB]\ * #,##0_);_([$THB]\ * \(#,##0\);_([$THB]\ * &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,23 +162,58 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -168,19 +221,58 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,100 +608,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2C8A59-F202-4AD9-84F8-135D4610397E}">
-  <dimension ref="B2:L20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:L30"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="J5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="J6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="E14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>34</v>
+      </c>
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
@@ -617,95 +741,229 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+      <c r="B15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="12">
         <v>6</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="11">
         <v>100</v>
       </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="E15" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="F15" s="9">
+        <v>3.25</v>
+      </c>
+      <c r="G15" s="8">
+        <v>295</v>
+      </c>
+      <c r="H15" s="8">
+        <v>384</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+      <c r="B16" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="12">
         <v>12</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="11">
         <v>120</v>
       </c>
-      <c r="F16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="E16" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3.25</v>
+      </c>
+      <c r="G16" s="8">
+        <v>295</v>
+      </c>
+      <c r="H16" s="8">
+        <v>384</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+      <c r="B17" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="12">
         <v>6</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="11">
         <v>100</v>
       </c>
-      <c r="J17" t="s">
+      <c r="E17" s="9">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9">
+        <v>4</v>
+      </c>
+      <c r="G17" s="8">
+        <v>354</v>
+      </c>
+      <c r="H17" s="8">
+        <v>472</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+      <c r="B18" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="12">
         <v>12</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="11">
         <v>120</v>
       </c>
-      <c r="J18" t="s">
+      <c r="E18" s="9">
+        <v>3</v>
+      </c>
+      <c r="F18" s="9">
+        <v>4</v>
+      </c>
+      <c r="G18" s="8">
+        <v>354</v>
+      </c>
+      <c r="H18" s="8">
+        <v>472</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="B19" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="12">
         <v>6</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="11">
         <v>120</v>
       </c>
+      <c r="E19" s="9">
+        <v>4</v>
+      </c>
+      <c r="F19" s="9">
+        <v>5.23</v>
+      </c>
+      <c r="G19" s="8">
+        <v>472</v>
+      </c>
+      <c r="H19" s="8">
+        <v>617</v>
+      </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+      <c r="B20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="12">
         <v>12</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="11">
         <v>140</v>
       </c>
+      <c r="E20" s="9">
+        <v>4</v>
+      </c>
+      <c r="F20" s="9">
+        <v>5.23</v>
+      </c>
+      <c r="G20" s="8">
+        <v>472</v>
+      </c>
+      <c r="H20" s="8">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9">
+        <v>4.75</v>
+      </c>
+      <c r="F21" s="9">
+        <v>6.25</v>
+      </c>
+      <c r="G21" s="8">
+        <v>561</v>
+      </c>
+      <c r="H21" s="8">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="J14:L14"/>
+    <mergeCell ref="B13:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>